--- a/duoki_editor/resources/data/blank/服装店-一般疑问句_问句认读-1-blank.xlsx
+++ b/duoki_editor/resources/data/blank/服装店-一般疑问句_问句认读-1-blank.xlsx
@@ -61,10 +61,10 @@
     <t>一般疑问句_认读_1_问_2</t>
   </si>
   <si>
-    <t>(一般疑问句_认读_1_问_3)</t>
-  </si>
-  <si>
-    <t>一般疑问句_认读_1_答</t>
+    <t>(一般疑问句_认读_1_问_答案)</t>
+  </si>
+  <si>
+    <t>一般疑问句_认读_1_帮助</t>
   </si>
   <si>
     <t>结束语_1</t>
@@ -106,13 +106,13 @@
     <t>我来帮你吧！ {sentence_question_en}</t>
   </si>
   <si>
-    <t>Great！挑战成功！20颗闪闪亮亮的魔法宝石，送给你们！现在我得去宝石精灵那里拿宝石了，下次再来找你们，再见！See you！</t>
-  </si>
-  <si>
-    <t>这次{npc2_name}帮了你，只能得到10颗宝石哦！我还有超级多的宝石，下次你们可要加油哦！</t>
-  </si>
-  <si>
-    <t>20|10</t>
+    <t>Great！挑战成功！10颗闪闪亮亮的魔法宝石，送给你们！现在我得去宝石精灵那里拿宝石了，下次再来找你们，再见！See you！</t>
+  </si>
+  <si>
+    <t>这次{npc2_name}帮了你，只能得到5颗宝石哦！我还有超级多的宝石，下次你们可要加油哦！</t>
+  </si>
+  <si>
+    <t>10|5</t>
   </si>
 </sst>
 </file>
